--- a/PVH.xlsx
+++ b/PVH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F85B7B-7733-458B-BAA3-33110BF0C2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803CD83D-FBD3-4F0F-8F2A-11109913DF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{4E82A43E-637D-4DBB-91B0-A5D722633EBD}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{4E82A43E-637D-4DBB-91B0-A5D722633EBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -40,6 +40,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={D51EE676-5C5B-4335-A546-EAAD45EEB1DD}</author>
+    <author>tc={711DCC9E-6314-48C0-8101-7AEAA9FA9195}</author>
     <author>tc={F0ACDF0F-CDA2-4712-9A7E-53F6389B265C}</author>
   </authors>
   <commentList>
@@ -51,7 +52,15 @@
     Changed sgment reporting</t>
       </text>
     </comment>
-    <comment ref="Z18" authorId="1" shapeId="0" xr:uid="{F0ACDF0F-CDA2-4712-9A7E-53F6389B265C}">
+    <comment ref="P18" authorId="1" shapeId="0" xr:uid="{711DCC9E-6314-48C0-8101-7AEAA9FA9195}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    439 Assets Impairment</t>
+      </text>
+    </comment>
+    <comment ref="Z18" authorId="2" shapeId="0" xr:uid="{F0ACDF0F-CDA2-4712-9A7E-53F6389B265C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -279,13 +288,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -332,6 +347,12 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -471,45 +492,45 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -855,6 +876,9 @@
   <threadedComment ref="Z8" dT="2026-05-15T11:58:36.19" personId="{08AA6270-0AA0-4052-82A4-EF407D925022}" id="{D51EE676-5C5B-4335-A546-EAAD45EEB1DD}">
     <text>Changed sgment reporting</text>
   </threadedComment>
+  <threadedComment ref="P18" dT="2026-09-04T08:57:54.20" personId="{08AA6270-0AA0-4052-82A4-EF407D925022}" id="{711DCC9E-6314-48C0-8101-7AEAA9FA9195}">
+    <text>439 Assets Impairment</text>
+  </threadedComment>
   <threadedComment ref="Z18" dT="2026-05-15T11:52:09.02" personId="{08AA6270-0AA0-4052-82A4-EF407D925022}" id="{F0ACDF0F-CDA2-4712-9A7E-53F6389B265C}">
     <text>479,5 mio Goowill impairment</text>
   </threadedComment>
@@ -884,7 +908,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="7">
-        <v>77.790000000000006</v>
+        <v>72.459999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -892,10 +916,10 @@
         <v>3</v>
       </c>
       <c r="J3" s="4">
-        <v>46.108091999999999</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>63</v>
+        <v>46.137833000000001</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -907,7 +931,7 @@
       </c>
       <c r="J4" s="4">
         <f>+J2*J3</f>
-        <v>3586.7484766800003</v>
+        <v>3343.1473791799999</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -918,10 +942,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="4">
-        <v>592.5</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>63</v>
+        <v>965.9</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -929,11 +953,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="4">
-        <f>12.9+2269.4</f>
-        <v>2282.3000000000002</v>
-      </c>
-      <c r="K6" s="25" t="s">
-        <v>63</v>
+        <v>2236.5</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -948,7 +971,7 @@
       </c>
       <c r="J7" s="4">
         <f>+J4-J5+J6</f>
-        <v>5276.54847668</v>
+        <v>4613.7473791800003</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1093,8 +1116,12 @@
         <v>1113.9000000000001</v>
       </c>
       <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
+      <c r="O3" s="4">
+        <v>946.1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>986.3</v>
+      </c>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
@@ -1191,8 +1218,12 @@
         <v>682.8</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
+      <c r="O4" s="4">
+        <v>602.9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>680.1</v>
+      </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -1289,8 +1320,12 @@
         <v>391.9</v>
       </c>
       <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
+      <c r="O5" s="4">
+        <v>387</v>
+      </c>
+      <c r="P5" s="4">
+        <v>343.7</v>
+      </c>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
@@ -1387,8 +1422,12 @@
         <v>1217.7</v>
       </c>
       <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
+      <c r="O6" s="4">
+        <v>1077.3</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1131.8</v>
+      </c>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
@@ -1481,8 +1520,12 @@
         <v>1018.2</v>
       </c>
       <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
+      <c r="O7" s="4">
+        <v>895.2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>913.3</v>
+      </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
@@ -1575,8 +1618,12 @@
         <v>58.4</v>
       </c>
       <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
+      <c r="O8" s="4">
+        <v>52.6</v>
+      </c>
+      <c r="P8" s="4">
+        <v>51.9</v>
+      </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
@@ -1671,8 +1718,12 @@
         <v>1257.5999999999999</v>
       </c>
       <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
+      <c r="O9" s="4">
+        <v>1067</v>
+      </c>
+      <c r="P9" s="4">
+        <v>954</v>
+      </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
@@ -1773,8 +1824,12 @@
         <v>760.7</v>
       </c>
       <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
+      <c r="O10" s="4">
+        <v>698.9</v>
+      </c>
+      <c r="P10" s="4">
+        <v>862</v>
+      </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
@@ -1875,8 +1930,12 @@
         <v>170.3</v>
       </c>
       <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
+      <c r="O11" s="4">
+        <v>170.1</v>
+      </c>
+      <c r="P11" s="4">
+        <v>194.1</v>
+      </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
@@ -1978,8 +2037,12 @@
         <v>931</v>
       </c>
       <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
+      <c r="O12" s="4">
+        <v>869</v>
+      </c>
+      <c r="P12" s="4">
+        <v>1056.0999999999999</v>
+      </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
@@ -2080,8 +2143,12 @@
         <v>105.7</v>
       </c>
       <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
+      <c r="O13" s="4">
+        <v>89.1</v>
+      </c>
+      <c r="P13" s="4">
+        <v>86.9</v>
+      </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
@@ -2182,8 +2249,12 @@
         <v>0</v>
       </c>
       <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0</v>
+      </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
@@ -2301,7 +2372,9 @@
       <c r="O15" s="6">
         <v>2025.1</v>
       </c>
-      <c r="P15" s="6"/>
+      <c r="P15" s="6">
+        <v>2097</v>
+      </c>
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
       <c r="S15" s="4"/>
@@ -2417,7 +2490,9 @@
       <c r="O16" s="4">
         <v>838.9</v>
       </c>
-      <c r="P16" s="4"/>
+      <c r="P16" s="4">
+        <v>775.2</v>
+      </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
@@ -2517,55 +2592,58 @@
         <v>1245.9000000000001</v>
       </c>
       <c r="I17" s="4">
-        <f>+I15-I16</f>
+        <f t="shared" ref="I17:P17" si="3">+I15-I16</f>
         <v>1316.6</v>
       </c>
       <c r="J17" s="4">
-        <f>+J15-J16</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K17" s="4">
-        <f>+K15-K16</f>
+        <f t="shared" si="3"/>
         <v>1161.6999999999998</v>
       </c>
       <c r="L17" s="4">
-        <f>+L15-L16</f>
+        <f t="shared" si="3"/>
         <v>1250.7999999999997</v>
       </c>
       <c r="M17" s="4">
-        <f>+M15-M16</f>
+        <f t="shared" si="3"/>
         <v>1292.8000000000002</v>
       </c>
       <c r="N17" s="4">
-        <f>+N15-N16</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O17" s="4">
-        <f>+O15-O16</f>
+        <f t="shared" si="3"/>
         <v>1186.1999999999998</v>
       </c>
-      <c r="P17" s="4"/>
+      <c r="P17" s="4">
+        <f t="shared" si="3"/>
+        <v>1321.8</v>
+      </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4">
-        <f t="shared" ref="T17:X17" si="3">+T15-T16</f>
+        <f t="shared" ref="T17:X17" si="4">+T15-T16</f>
         <v>0</v>
       </c>
       <c r="U17" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V17" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W17" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5122.8999999999987</v>
       </c>
       <c r="X17" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5363.2000000000007</v>
       </c>
       <c r="Y17" s="4">
@@ -2662,7 +2740,10 @@
       <c r="O18" s="4">
         <v>1074.4000000000001</v>
       </c>
-      <c r="P18" s="4"/>
+      <c r="P18" s="4">
+        <f>1112.5+439</f>
+        <v>1551.5</v>
+      </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
@@ -2739,11 +2820,11 @@
         <v>27</v>
       </c>
       <c r="C19" s="4">
-        <f t="shared" ref="C19:D19" si="4">+C17-C18</f>
+        <f t="shared" ref="C19:D19" si="5">+C17-C18</f>
         <v>0</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E19" s="4">
@@ -2751,19 +2832,19 @@
         <v>215.60000000000014</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" ref="F19:I19" si="5">+F17-F18</f>
+        <f t="shared" ref="F19:I19" si="6">+F17-F18</f>
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>181.40000000000009</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>162.60000000000014</v>
       </c>
       <c r="I19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>162.59999999999991</v>
       </c>
       <c r="J19" s="4">
@@ -2779,47 +2860,50 @@
         <v>121.89999999999964</v>
       </c>
       <c r="M19" s="4">
-        <f t="shared" ref="M19:O19" si="6">+M17-M18</f>
+        <f t="shared" ref="M19:P19" si="7">+M17-M18</f>
         <v>171.80000000000018</v>
       </c>
       <c r="N19" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O19" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>111.79999999999973</v>
       </c>
-      <c r="P19" s="4"/>
+      <c r="P19" s="4">
+        <f t="shared" si="7"/>
+        <v>-229.70000000000005</v>
+      </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4">
-        <f t="shared" ref="T19" si="7">+T17-T18</f>
+        <f t="shared" ref="T19" si="8">+T17-T18</f>
         <v>0</v>
       </c>
       <c r="U19" s="4">
-        <f t="shared" ref="U19" si="8">+U17-U18</f>
+        <f t="shared" ref="U19" si="9">+U17-U18</f>
         <v>0</v>
       </c>
       <c r="V19" s="4">
-        <f t="shared" ref="V19" si="9">+V17-V18</f>
+        <f t="shared" ref="V19" si="10">+V17-V18</f>
         <v>0</v>
       </c>
       <c r="W19" s="4">
-        <f t="shared" ref="W19" si="10">+W17-W18</f>
+        <f t="shared" ref="W19" si="11">+W17-W18</f>
         <v>745.49999999999909</v>
       </c>
       <c r="X19" s="4">
-        <f t="shared" ref="X19" si="11">+X17-X18</f>
+        <f t="shared" ref="X19" si="12">+X17-X18</f>
         <v>820.60000000000036</v>
       </c>
       <c r="Y19" s="4">
-        <f t="shared" ref="Y19:Z19" si="12">+Y17-Y18</f>
+        <f t="shared" ref="Y19:Z19" si="13">+Y17-Y18</f>
         <v>731.20000000000164</v>
       </c>
       <c r="Z19" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>177</v>
       </c>
       <c r="AA19" s="4"/>
@@ -2907,7 +2991,9 @@
       <c r="O20" s="4">
         <v>-0.8</v>
       </c>
-      <c r="P20" s="4"/>
+      <c r="P20" s="4">
+        <v>-0.6</v>
+      </c>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
@@ -3012,7 +3098,9 @@
       <c r="O21" s="4">
         <v>0</v>
       </c>
-      <c r="P21" s="4"/>
+      <c r="P21" s="4">
+        <v>25.4</v>
+      </c>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
@@ -3116,7 +3204,9 @@
       <c r="O22" s="4">
         <v>13.3</v>
       </c>
-      <c r="P22" s="4"/>
+      <c r="P22" s="4">
+        <v>14</v>
+      </c>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
@@ -3220,7 +3310,9 @@
       <c r="O23" s="4">
         <v>22.7</v>
       </c>
-      <c r="P23" s="4"/>
+      <c r="P23" s="4">
+        <v>22.3</v>
+      </c>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
@@ -3324,7 +3416,9 @@
       <c r="O24" s="4">
         <v>6.9</v>
       </c>
-      <c r="P24" s="4"/>
+      <c r="P24" s="4">
+        <v>10.6</v>
+      </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
@@ -3400,87 +3494,90 @@
         <v>30</v>
       </c>
       <c r="C25" s="4">
-        <f>+C19+SUM(C20:C22)-C23+C24</f>
+        <f t="shared" ref="C25:P25" si="14">+C19+SUM(C20:C22)-C23+C24</f>
         <v>0</v>
       </c>
       <c r="D25" s="4">
-        <f>+D19+SUM(D20:D22)-D23+D24</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E25" s="4">
-        <f>+E19+SUM(E20:E22)-E23+E24</f>
+        <f t="shared" si="14"/>
         <v>207.60000000000011</v>
       </c>
       <c r="F25" s="4">
-        <f>+F19+SUM(F20:F22)-F23+F24</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f>+G19+SUM(G20:G22)-G23+G24</f>
+        <f t="shared" si="14"/>
         <v>187.40000000000006</v>
       </c>
       <c r="H25" s="4">
-        <f>+H19+SUM(H20:H22)-H23+H24</f>
+        <f t="shared" si="14"/>
         <v>154.80000000000013</v>
       </c>
       <c r="I25" s="4">
-        <f>+I19+SUM(I20:I22)-I23+I24</f>
+        <f t="shared" si="14"/>
         <v>166.99999999999991</v>
       </c>
       <c r="J25" s="4">
-        <f>+J19+SUM(J20:J22)-J23+J24</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K25" s="4">
-        <f>+K19+SUM(K20:K22)-K23+K24</f>
+        <f t="shared" si="14"/>
         <v>-349.60000000000025</v>
       </c>
       <c r="L25" s="4">
-        <f>+L19+SUM(L20:L22)-L23+L24</f>
+        <f t="shared" si="14"/>
         <v>111.19999999999965</v>
       </c>
       <c r="M25" s="4">
-        <f>+M19+SUM(M20:M22)-M23+M24</f>
+        <f t="shared" si="14"/>
         <v>160.30000000000018</v>
       </c>
       <c r="N25" s="4">
-        <f>+N19+SUM(N20:N22)-N23+N24</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O25" s="4">
-        <f>+O19+SUM(O20:O22)-O23+O24</f>
+        <f t="shared" si="14"/>
         <v>108.49999999999973</v>
       </c>
-      <c r="P25" s="4"/>
+      <c r="P25" s="4">
+        <f t="shared" si="14"/>
+        <v>-202.60000000000005</v>
+      </c>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4">
-        <f>+T19+SUM(T20:T22)-T23+T24</f>
+        <f t="shared" ref="T25:Z25" si="15">+T19+SUM(T20:T22)-T23+T24</f>
         <v>0</v>
       </c>
       <c r="U25" s="4">
-        <f>+U19+SUM(U20:U22)-U23+U24</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V25" s="4">
-        <f>+V19+SUM(V20:V22)-V23+V24</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="W25" s="4">
-        <f>+W19+SUM(W20:W22)-W23+W24</f>
+        <f t="shared" si="15"/>
         <v>388.19999999999902</v>
       </c>
       <c r="X25" s="4">
-        <f>+X19+SUM(X20:X22)-X23+X24</f>
+        <f t="shared" si="15"/>
         <v>841.00000000000045</v>
       </c>
       <c r="Y25" s="4">
-        <f>+Y19+SUM(Y20:Y22)-Y23+Y24</f>
+        <f t="shared" si="15"/>
         <v>705.70000000000175</v>
       </c>
       <c r="Z25" s="4">
-        <f>+Z19+SUM(Z20:Z22)-Z23+Z24</f>
+        <f t="shared" si="15"/>
         <v>151.29999999999998</v>
       </c>
       <c r="AA25" s="4"/>
@@ -3568,7 +3665,9 @@
       <c r="O26" s="4">
         <v>20.5</v>
       </c>
-      <c r="P26" s="4"/>
+      <c r="P26" s="4">
+        <v>-99.7</v>
+      </c>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
@@ -3644,27 +3743,27 @@
         <v>32</v>
       </c>
       <c r="C27" s="4">
-        <f t="shared" ref="C27:H27" si="13">+C25-C26</f>
+        <f t="shared" ref="C27:H27" si="16">+C25-C26</f>
         <v>0</v>
       </c>
       <c r="D27" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="E27" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>161.60000000000011</v>
       </c>
       <c r="F27" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G27" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>151.40000000000006</v>
       </c>
       <c r="H27" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>158.00000000000011</v>
       </c>
       <c r="I27" s="4">
@@ -3672,47 +3771,50 @@
         <v>131.89999999999992</v>
       </c>
       <c r="J27" s="4">
-        <f t="shared" ref="J27:N27" si="14">+J25-J26</f>
+        <f t="shared" ref="J27:N27" si="17">+J25-J26</f>
         <v>0</v>
       </c>
       <c r="K27" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-44.800000000000239</v>
       </c>
       <c r="L27" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>224.19999999999965</v>
       </c>
       <c r="M27" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>4.2000000000001876</v>
       </c>
       <c r="N27" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O27" s="4">
-        <f t="shared" ref="O27" si="15">+O25-O26</f>
+        <f t="shared" ref="O27:P27" si="18">+O25-O26</f>
         <v>87.99999999999973</v>
       </c>
-      <c r="P27" s="4"/>
+      <c r="P27" s="4">
+        <f t="shared" si="18"/>
+        <v>-102.90000000000005</v>
+      </c>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
       <c r="T27" s="4">
-        <f t="shared" ref="T27:W27" si="16">+T25-T26</f>
+        <f t="shared" ref="T27:W27" si="19">+T25-T26</f>
         <v>0</v>
       </c>
       <c r="U27" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="V27" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="W27" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>200.39999999999901</v>
       </c>
       <c r="X27" s="4">
@@ -3720,11 +3822,11 @@
         <v>723.60000000000048</v>
       </c>
       <c r="Y27" s="4">
-        <f t="shared" ref="Y27:Z27" si="17">+Y25-Y26</f>
+        <f t="shared" ref="Y27:Z27" si="20">+Y25-Y26</f>
         <v>598.50000000000171</v>
       </c>
       <c r="Z27" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>25.299999999999983</v>
       </c>
       <c r="AA27" s="4"/>
@@ -3861,11 +3963,11 @@
         <v>33</v>
       </c>
       <c r="C29" s="7" t="e">
-        <f t="shared" ref="C29:D29" si="18">+C27/C30</f>
+        <f t="shared" ref="C29:D29" si="21">+C27/C30</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D29" s="7" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E29" s="7">
@@ -3873,78 +3975,78 @@
         <v>2.6799336650082939</v>
       </c>
       <c r="F29" s="7" t="e">
-        <f t="shared" ref="F29:P29" si="19">+F27/F30</f>
+        <f t="shared" ref="F29:P29" si="22">+F27/F30</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>2.5924657534246585</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>2.7964601769911526</v>
       </c>
       <c r="I29" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>2.3637992831541204</v>
       </c>
       <c r="J29" s="7" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K29" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>-0.8767123287671279</v>
       </c>
       <c r="L29" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>4.6611226611226533</v>
       </c>
       <c r="M29" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>8.8794926004232305E-2</v>
       </c>
       <c r="N29" s="7" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O29" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>1.9172113289760291</v>
       </c>
-      <c r="P29" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+      <c r="P29" s="7">
+        <f t="shared" si="22"/>
+        <v>-2.232104121475055</v>
       </c>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
       <c r="S29" s="8"/>
       <c r="T29" s="7" t="e">
-        <f t="shared" ref="T29:Z29" si="20">+T27/T30</f>
+        <f t="shared" ref="T29:Z29" si="23">+T27/T30</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U29" s="7" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V29" s="7" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W29" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>3.0502283105022681</v>
       </c>
       <c r="X29" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>11.86229508196722</v>
       </c>
       <c r="Y29" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>10.68750000000003</v>
       </c>
       <c r="Z29" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.52598752598752563</v>
       </c>
       <c r="AA29" s="8"/>
@@ -4003,10 +4105,12 @@
         <v>47.3</v>
       </c>
       <c r="N30" s="8"/>
-      <c r="O30" s="26">
+      <c r="O30" s="25">
         <v>45.9</v>
       </c>
-      <c r="P30" s="8"/>
+      <c r="P30" s="8">
+        <v>46.1</v>
+      </c>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
       <c r="S30" s="8"/>
@@ -4111,71 +4215,71 @@
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
       <c r="G32" s="22" t="e">
-        <f>+G15/C15-1</f>
+        <f t="shared" ref="G32:N32" si="24">+G15/C15-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H32" s="22" t="e">
-        <f>+H15/D15-1</f>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I32" s="22">
-        <f>+I15/E15-1</f>
+        <f t="shared" si="24"/>
         <v>-4.5621905285877618E-2</v>
       </c>
       <c r="J32" s="22" t="e">
-        <f>+J15/F15-1</f>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K32" s="22">
-        <f>+K15/G15-1</f>
+        <f t="shared" si="24"/>
         <v>1.6240586095598974E-2</v>
       </c>
       <c r="L32" s="22">
-        <f>+L15/H15-1</f>
+        <f t="shared" si="24"/>
         <v>4.478619293255548E-2</v>
       </c>
       <c r="M32" s="22">
-        <f>+M15/I15-1</f>
+        <f t="shared" si="24"/>
         <v>1.7382821160924156E-2</v>
       </c>
       <c r="N32" s="22" t="e">
-        <f>+N15/J15-1</f>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O32" s="22">
-        <f t="shared" ref="O32:P32" si="21">+O15/K15-1</f>
+        <f t="shared" ref="O32:P32" si="25">+O15/K15-1</f>
         <v>2.0921556765476801E-2</v>
       </c>
       <c r="P32" s="22">
-        <f t="shared" si="21"/>
-        <v>-1</v>
+        <f t="shared" si="25"/>
+        <v>-3.2392026578073052E-2</v>
       </c>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="8"/>
       <c r="T32" s="8"/>
       <c r="U32" s="22" t="e">
-        <f>+U15/T15-1</f>
+        <f t="shared" ref="U32:Z32" si="26">+U15/T15-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V32" s="22" t="e">
-        <f>+V15/U15-1</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W32" s="22" t="e">
-        <f>+W15/V15-1</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X32" s="22">
-        <f>+X15/W15-1</f>
+        <f t="shared" si="26"/>
         <v>2.1442343919682916E-2</v>
       </c>
       <c r="Y32" s="22">
-        <f>+Y15/X15-1</f>
+        <f t="shared" si="26"/>
         <v>-6.127341961660715E-2</v>
       </c>
       <c r="Z32" s="22">
-        <f>+Z15/Y15-1</f>
+        <f t="shared" si="26"/>
         <v>3.4358423187601739E-2</v>
       </c>
       <c r="AA32" s="8"/>
@@ -4209,87 +4313,87 @@
         <v>38</v>
       </c>
       <c r="C33" s="9" t="e">
-        <f>+C17/C15</f>
+        <f t="shared" ref="C33:N33" si="27">+C17/C15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D33" s="9" t="e">
-        <f>+D17/D15</f>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E33" s="9">
-        <f>+E17/E15</f>
+        <f t="shared" si="27"/>
         <v>0.56684582504549497</v>
       </c>
       <c r="F33" s="9" t="e">
-        <f>+F17/F15</f>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G33" s="9">
-        <f>+G17/G15</f>
+        <f t="shared" si="27"/>
         <v>0.61411957579794041</v>
       </c>
       <c r="H33" s="9">
-        <f>+H17/H15</f>
+        <f t="shared" si="27"/>
         <v>0.60063635925372416</v>
       </c>
       <c r="I33" s="9">
-        <f>+I17/I15</f>
+        <f t="shared" si="27"/>
         <v>0.58383220256307922</v>
       </c>
       <c r="J33" s="9" t="e">
-        <f>+J17/J15</f>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="9">
-        <f>+K17/K15</f>
+        <f t="shared" si="27"/>
         <v>0.58565234926396448</v>
       </c>
       <c r="L33" s="9">
-        <f>+L17/L15</f>
+        <f t="shared" si="27"/>
         <v>0.5771502399409375</v>
       </c>
       <c r="M33" s="9">
-        <f>+M17/M15</f>
+        <f t="shared" si="27"/>
         <v>0.56348341542082558</v>
       </c>
       <c r="N33" s="9" t="e">
-        <f>+N17/N15</f>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" ref="O33:P33" si="22">+O17/O15</f>
+        <f t="shared" ref="O33:P33" si="28">+O17/O15</f>
         <v>0.58574885190854764</v>
       </c>
-      <c r="P33" s="9" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+      <c r="P33" s="9">
+        <f t="shared" si="28"/>
+        <v>0.63032904148783975</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="8"/>
       <c r="T33" s="8"/>
       <c r="U33" s="9" t="e">
-        <f>+U17/U15</f>
+        <f t="shared" ref="U33:Z33" si="29">+U17/U15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V33" s="9" t="e">
-        <f>+V17/V15</f>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W33" s="9">
-        <f>+W17/W15</f>
+        <f t="shared" si="29"/>
         <v>0.56768467010926171</v>
       </c>
       <c r="X33" s="9">
-        <f>+X17/X15</f>
+        <f t="shared" si="29"/>
         <v>0.58183711771917079</v>
       </c>
       <c r="Y33" s="9">
-        <f>+Y17/Y15</f>
+        <f t="shared" si="29"/>
         <v>0.59430942227461325</v>
       </c>
       <c r="Z33" s="9">
-        <f>+Z17/Z15</f>
+        <f t="shared" si="29"/>
         <v>0.57524971509016554</v>
       </c>
       <c r="AA33" s="8"/>
@@ -4323,87 +4427,87 @@
         <v>39</v>
       </c>
       <c r="C34" s="9" t="e">
-        <f>+C19/C15</f>
+        <f t="shared" ref="C34:N34" si="30">+C19/C15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D34" s="9" t="e">
-        <f>+D19/D15</f>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E34" s="9">
-        <f>+E19/E15</f>
+        <f t="shared" si="30"/>
         <v>9.1243810571755096E-2</v>
       </c>
       <c r="F34" s="9" t="e">
-        <f>+F19/F15</f>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G34" s="9">
-        <f>+G19/G15</f>
+        <f t="shared" si="30"/>
         <v>9.2935088887750442E-2</v>
       </c>
       <c r="H34" s="9">
-        <f>+H19/H15</f>
+        <f t="shared" si="30"/>
         <v>7.8387889890565554E-2</v>
       </c>
       <c r="I34" s="9">
-        <f>+I19/I15</f>
+        <f t="shared" si="30"/>
         <v>7.2103232672608722E-2</v>
       </c>
       <c r="J34" s="9" t="e">
-        <f>+J19/J15</f>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K34" s="9">
-        <f>+K19/K15</f>
+        <f t="shared" si="30"/>
         <v>-0.17226255293405943</v>
       </c>
       <c r="L34" s="9">
-        <f>+L19/L15</f>
+        <f t="shared" si="30"/>
         <v>5.6247692875599692E-2</v>
       </c>
       <c r="M34" s="9">
-        <f>+M19/M15</f>
+        <f t="shared" si="30"/>
         <v>7.4881227389617819E-2</v>
       </c>
       <c r="N34" s="9" t="e">
-        <f>+N19/N15</f>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" ref="O34:P34" si="23">+O19/O15</f>
+        <f t="shared" ref="O34:P34" si="31">+O19/O15</f>
         <v>5.5207150264184351E-2</v>
       </c>
-      <c r="P34" s="9" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+      <c r="P34" s="9">
+        <f t="shared" si="31"/>
+        <v>-0.10953743443013832</v>
       </c>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="8"/>
       <c r="T34" s="8"/>
       <c r="U34" s="9" t="e">
-        <f>+U19/U15</f>
+        <f t="shared" ref="U34:Z34" si="32">+U19/U15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V34" s="9" t="e">
-        <f>+V19/V15</f>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W34" s="9">
-        <f>+W19/W15</f>
+        <f t="shared" si="32"/>
         <v>8.26112009928857E-2</v>
       </c>
       <c r="X34" s="9">
-        <f>+X19/X15</f>
+        <f t="shared" si="32"/>
         <v>8.9024377013788722E-2</v>
       </c>
       <c r="Y34" s="9">
-        <f>+Y19/Y15</f>
+        <f t="shared" si="32"/>
         <v>8.4503461267320959E-2</v>
       </c>
       <c r="Z34" s="9">
-        <f>+Z19/Z15</f>
+        <f t="shared" si="32"/>
         <v>1.9776094388952201E-2</v>
       </c>
       <c r="AA34" s="8"/>
@@ -4437,27 +4541,27 @@
         <v>40</v>
       </c>
       <c r="C35" s="9" t="e">
-        <f t="shared" ref="C35:H35" si="24">+C26/C25</f>
+        <f t="shared" ref="C35:H35" si="33">+C26/C25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D35" s="9" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E35" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>0.22157996146435441</v>
       </c>
       <c r="F35" s="9" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G35" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>0.19210245464247591</v>
       </c>
       <c r="H35" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>-2.0671834625322981E-2</v>
       </c>
       <c r="I35" s="9">
@@ -4465,59 +4569,59 @@
         <v>0.21017964071856299</v>
       </c>
       <c r="J35" s="9" t="e">
-        <f t="shared" ref="J35:L35" si="25">+J26/J25</f>
+        <f t="shared" ref="J35:L35" si="34">+J26/J25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0.87185354691075456</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>-1.0161870503597155</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" ref="M35:N35" si="26">+M26/M25</f>
+        <f t="shared" ref="M35:N35" si="35">+M26/M25</f>
         <v>0.97379912663755341</v>
       </c>
       <c r="N35" s="9" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" ref="O35:P35" si="27">+O26/O25</f>
+        <f t="shared" ref="O35:P35" si="36">+O26/O25</f>
         <v>0.18894009216589908</v>
       </c>
-      <c r="P35" s="9" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
+      <c r="P35" s="9">
+        <f t="shared" si="36"/>
+        <v>0.49210266535044411</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="8"/>
       <c r="T35" s="8"/>
       <c r="U35" s="9" t="e">
-        <f t="shared" ref="U35:Y35" si="28">+U26/U25</f>
+        <f t="shared" ref="U35:Y35" si="37">+U26/U25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V35" s="9" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W35" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.48377125193199505</v>
       </c>
       <c r="X35" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.13959571938168841</v>
       </c>
       <c r="Y35" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.15190590902649814</v>
       </c>
       <c r="Z35" s="9">
-        <f t="shared" ref="Z35" si="29">+Z26/Z25</f>
+        <f t="shared" ref="Z35" si="38">+Z26/Z25</f>
         <v>0.83278255122273637</v>
       </c>
       <c r="AA35" s="8"/>
